--- a/2-Section- Basic Excel/data/04 Restaurant Sales.xlsx
+++ b/2-Section- Basic Excel/data/04 Restaurant Sales.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29902"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sumit\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a6ce4a7617f1ad9/Desktop/courses/Data Analytics/2-Section- Basic Excel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB2AD424-2D60-4E2A-89EA-9C030A16242E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{FB2AD424-2D60-4E2A-89EA-9C030A16242E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77B5EC31-BE83-4599-8B33-A3F0485335D3}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{66301FCA-EA2A-4B3B-9A5C-535C597A10AA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{66301FCA-EA2A-4B3B-9A5C-535C597A10AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Restaurant Sales" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurant Sales'!$A$1:$J$1001</definedName>
@@ -30,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5010" uniqueCount="1052">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5011" uniqueCount="1053">
   <si>
     <t>Transaction ID</t>
   </si>
@@ -3198,6 +3197,9 @@
   </si>
   <si>
     <t>RST-31000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average rating </t>
   </si>
 </sst>
 </file>
@@ -3594,21 +3596,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91B0B381-6FE6-4B24-8840-A2752167A525}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:J1001"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="17.109375" customWidth="1"/>
+    <col min="3" max="4" width="24.109375" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.21875" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" customWidth="1"/>
+    <col min="9" max="9" width="14.88671875" customWidth="1"/>
+    <col min="10" max="10" width="21.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -3736,7 +3736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -3800,7 +3800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -3832,7 +3832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -3896,7 +3896,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -3992,7 +3992,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -4088,7 +4088,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -4120,7 +4120,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>51</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>54</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>56</v>
       </c>
@@ -4248,7 +4248,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -4376,7 +4376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -4408,7 +4408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -4440,7 +4440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -4472,7 +4472,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -4504,7 +4504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -4568,7 +4568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -4696,7 +4696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -4728,7 +4728,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>78</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>80</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>81</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>82</v>
       </c>
@@ -4856,7 +4856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>84</v>
       </c>
@@ -4888,7 +4888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>85</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>86</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -4984,7 +4984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>88</v>
       </c>
@@ -5016,7 +5016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -5048,7 +5048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>90</v>
       </c>
@@ -5080,7 +5080,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>91</v>
       </c>
@@ -5112,7 +5112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>92</v>
       </c>
@@ -5144,7 +5144,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>93</v>
       </c>
@@ -5176,7 +5176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>94</v>
       </c>
@@ -5208,7 +5208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>95</v>
       </c>
@@ -5240,7 +5240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>96</v>
       </c>
@@ -5272,7 +5272,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>98</v>
       </c>
@@ -5304,7 +5304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>99</v>
       </c>
@@ -5336,7 +5336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>100</v>
       </c>
@@ -5368,7 +5368,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>101</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>102</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>103</v>
       </c>
@@ -5464,7 +5464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>104</v>
       </c>
@@ -5496,7 +5496,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>105</v>
       </c>
@@ -5528,7 +5528,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>106</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>107</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>108</v>
       </c>
@@ -5624,7 +5624,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>109</v>
       </c>
@@ -5656,7 +5656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>110</v>
       </c>
@@ -5688,7 +5688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>111</v>
       </c>
@@ -5720,7 +5720,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>113</v>
       </c>
@@ -5752,7 +5752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>114</v>
       </c>
@@ -5784,7 +5784,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>115</v>
       </c>
@@ -5816,7 +5816,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>116</v>
       </c>
@@ -5848,7 +5848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>117</v>
       </c>
@@ -5880,7 +5880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>118</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>120</v>
       </c>
@@ -5944,7 +5944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>121</v>
       </c>
@@ -5976,7 +5976,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>122</v>
       </c>
@@ -6008,7 +6008,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>123</v>
       </c>
@@ -6040,7 +6040,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>124</v>
       </c>
@@ -6072,7 +6072,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>125</v>
       </c>
@@ -6104,7 +6104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>126</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>127</v>
       </c>
@@ -6168,7 +6168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>128</v>
       </c>
@@ -6200,7 +6200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>129</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>130</v>
       </c>
@@ -6264,7 +6264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>131</v>
       </c>
@@ -6296,7 +6296,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>132</v>
       </c>
@@ -6328,7 +6328,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>133</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>134</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -6424,7 +6424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>136</v>
       </c>
@@ -6456,7 +6456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>137</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>138</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>139</v>
       </c>
@@ -6552,7 +6552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>140</v>
       </c>
@@ -6584,7 +6584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>141</v>
       </c>
@@ -6616,7 +6616,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>143</v>
       </c>
@@ -6648,7 +6648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>144</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>145</v>
       </c>
@@ -6712,7 +6712,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>146</v>
       </c>
@@ -6744,7 +6744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>147</v>
       </c>
@@ -6776,7 +6776,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>148</v>
       </c>
@@ -6808,7 +6808,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>149</v>
       </c>
@@ -6840,7 +6840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>150</v>
       </c>
@@ -6872,7 +6872,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>151</v>
       </c>
@@ -6904,7 +6904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>152</v>
       </c>
@@ -6936,7 +6936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>153</v>
       </c>
@@ -6968,7 +6968,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>154</v>
       </c>
@@ -7000,7 +7000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>155</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>156</v>
       </c>
@@ -7064,7 +7064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>157</v>
       </c>
@@ -7096,7 +7096,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>158</v>
       </c>
@@ -7128,7 +7128,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>159</v>
       </c>
@@ -7160,7 +7160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>160</v>
       </c>
@@ -7192,7 +7192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>161</v>
       </c>
@@ -7224,7 +7224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>162</v>
       </c>
@@ -7256,7 +7256,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>163</v>
       </c>
@@ -7288,7 +7288,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>164</v>
       </c>
@@ -7320,7 +7320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>165</v>
       </c>
@@ -7352,7 +7352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>166</v>
       </c>
@@ -7384,7 +7384,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>167</v>
       </c>
@@ -7416,7 +7416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>168</v>
       </c>
@@ -7448,7 +7448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>169</v>
       </c>
@@ -7480,7 +7480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>170</v>
       </c>
@@ -7512,7 +7512,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>171</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>172</v>
       </c>
@@ -7576,7 +7576,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>173</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>174</v>
       </c>
@@ -7640,7 +7640,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>175</v>
       </c>
@@ -7672,7 +7672,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>177</v>
       </c>
@@ -7704,7 +7704,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>178</v>
       </c>
@@ -7736,7 +7736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>179</v>
       </c>
@@ -7768,7 +7768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>180</v>
       </c>
@@ -7800,7 +7800,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>181</v>
       </c>
@@ -7832,7 +7832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>182</v>
       </c>
@@ -7864,7 +7864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>183</v>
       </c>
@@ -7896,7 +7896,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>184</v>
       </c>
@@ -7928,7 +7928,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>185</v>
       </c>
@@ -7960,7 +7960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>186</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>187</v>
       </c>
@@ -8024,7 +8024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>188</v>
       </c>
@@ -8056,7 +8056,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>189</v>
       </c>
@@ -8088,7 +8088,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>190</v>
       </c>
@@ -8120,7 +8120,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>191</v>
       </c>
@@ -8152,7 +8152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>192</v>
       </c>
@@ -8184,7 +8184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>193</v>
       </c>
@@ -8216,7 +8216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>194</v>
       </c>
@@ -8248,7 +8248,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>195</v>
       </c>
@@ -8280,7 +8280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>196</v>
       </c>
@@ -8312,7 +8312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>197</v>
       </c>
@@ -8344,7 +8344,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>198</v>
       </c>
@@ -8376,7 +8376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>199</v>
       </c>
@@ -8408,7 +8408,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>200</v>
       </c>
@@ -8440,7 +8440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>201</v>
       </c>
@@ -8472,7 +8472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>202</v>
       </c>
@@ -8504,7 +8504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>203</v>
       </c>
@@ -8536,7 +8536,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>204</v>
       </c>
@@ -8568,7 +8568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>205</v>
       </c>
@@ -8600,7 +8600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>206</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>207</v>
       </c>
@@ -8664,7 +8664,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>208</v>
       </c>
@@ -8696,7 +8696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>209</v>
       </c>
@@ -8728,7 +8728,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>210</v>
       </c>
@@ -8760,7 +8760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>211</v>
       </c>
@@ -8792,7 +8792,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>212</v>
       </c>
@@ -8824,7 +8824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>213</v>
       </c>
@@ -8856,7 +8856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>214</v>
       </c>
@@ -8888,7 +8888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>215</v>
       </c>
@@ -8920,7 +8920,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>216</v>
       </c>
@@ -8952,7 +8952,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>217</v>
       </c>
@@ -8984,7 +8984,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>218</v>
       </c>
@@ -9016,7 +9016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>219</v>
       </c>
@@ -9048,7 +9048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>220</v>
       </c>
@@ -9080,7 +9080,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>222</v>
       </c>
@@ -9112,7 +9112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>223</v>
       </c>
@@ -9144,7 +9144,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>224</v>
       </c>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>225</v>
       </c>
@@ -9208,7 +9208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>226</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>227</v>
       </c>
@@ -9272,7 +9272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>228</v>
       </c>
@@ -9304,7 +9304,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>229</v>
       </c>
@@ -9336,7 +9336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>230</v>
       </c>
@@ -9368,7 +9368,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>231</v>
       </c>
@@ -9400,7 +9400,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>232</v>
       </c>
@@ -9432,7 +9432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>233</v>
       </c>
@@ -9464,7 +9464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>234</v>
       </c>
@@ -9496,7 +9496,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>235</v>
       </c>
@@ -9528,7 +9528,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>236</v>
       </c>
@@ -9560,7 +9560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>237</v>
       </c>
@@ -9592,7 +9592,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>238</v>
       </c>
@@ -9624,7 +9624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>239</v>
       </c>
@@ -9656,7 +9656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>240</v>
       </c>
@@ -9688,7 +9688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>241</v>
       </c>
@@ -9720,7 +9720,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>242</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>243</v>
       </c>
@@ -9784,7 +9784,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>244</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>245</v>
       </c>
@@ -9848,7 +9848,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>246</v>
       </c>
@@ -9880,7 +9880,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>247</v>
       </c>
@@ -9912,7 +9912,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>248</v>
       </c>
@@ -9944,7 +9944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>249</v>
       </c>
@@ -9976,7 +9976,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>250</v>
       </c>
@@ -10008,7 +10008,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>251</v>
       </c>
@@ -10040,7 +10040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>252</v>
       </c>
@@ -10072,7 +10072,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>253</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>254</v>
       </c>
@@ -10136,7 +10136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>255</v>
       </c>
@@ -10168,7 +10168,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>256</v>
       </c>
@@ -10200,7 +10200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>257</v>
       </c>
@@ -10232,7 +10232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>258</v>
       </c>
@@ -10264,7 +10264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>259</v>
       </c>
@@ -10296,7 +10296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>260</v>
       </c>
@@ -10328,7 +10328,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>261</v>
       </c>
@@ -10360,7 +10360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>262</v>
       </c>
@@ -10392,7 +10392,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>263</v>
       </c>
@@ -10424,7 +10424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>264</v>
       </c>
@@ -10456,7 +10456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>265</v>
       </c>
@@ -10488,7 +10488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>266</v>
       </c>
@@ -10520,7 +10520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>267</v>
       </c>
@@ -10552,7 +10552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>268</v>
       </c>
@@ -10584,7 +10584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>269</v>
       </c>
@@ -10616,7 +10616,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>270</v>
       </c>
@@ -10648,7 +10648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>271</v>
       </c>
@@ -10680,7 +10680,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>272</v>
       </c>
@@ -10712,7 +10712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>273</v>
       </c>
@@ -10744,7 +10744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>274</v>
       </c>
@@ -10776,7 +10776,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>275</v>
       </c>
@@ -10808,7 +10808,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>276</v>
       </c>
@@ -10840,7 +10840,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>277</v>
       </c>
@@ -10872,7 +10872,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>278</v>
       </c>
@@ -10904,7 +10904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>279</v>
       </c>
@@ -10936,7 +10936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>280</v>
       </c>
@@ -10968,7 +10968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>281</v>
       </c>
@@ -11000,7 +11000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>282</v>
       </c>
@@ -11032,7 +11032,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>283</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>284</v>
       </c>
@@ -11096,7 +11096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>285</v>
       </c>
@@ -11128,7 +11128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>286</v>
       </c>
@@ -11160,7 +11160,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>287</v>
       </c>
@@ -11192,7 +11192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>288</v>
       </c>
@@ -11224,7 +11224,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>289</v>
       </c>
@@ -11256,7 +11256,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>290</v>
       </c>
@@ -11288,7 +11288,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>291</v>
       </c>
@@ -11320,7 +11320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>292</v>
       </c>
@@ -11352,7 +11352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>293</v>
       </c>
@@ -11384,7 +11384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>294</v>
       </c>
@@ -11416,7 +11416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>295</v>
       </c>
@@ -11448,7 +11448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>296</v>
       </c>
@@ -11480,7 +11480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>297</v>
       </c>
@@ -11512,7 +11512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>298</v>
       </c>
@@ -11544,7 +11544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>299</v>
       </c>
@@ -11576,7 +11576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>300</v>
       </c>
@@ -11608,7 +11608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>301</v>
       </c>
@@ -11640,7 +11640,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>302</v>
       </c>
@@ -11672,7 +11672,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>303</v>
       </c>
@@ -11704,7 +11704,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>304</v>
       </c>
@@ -11736,7 +11736,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>305</v>
       </c>
@@ -11768,7 +11768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>306</v>
       </c>
@@ -11800,7 +11800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>307</v>
       </c>
@@ -11832,7 +11832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>308</v>
       </c>
@@ -11864,7 +11864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>309</v>
       </c>
@@ -11896,7 +11896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>310</v>
       </c>
@@ -11928,7 +11928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>311</v>
       </c>
@@ -11960,7 +11960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>312</v>
       </c>
@@ -11992,7 +11992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>313</v>
       </c>
@@ -12024,7 +12024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>314</v>
       </c>
@@ -12056,7 +12056,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>315</v>
       </c>
@@ -12088,7 +12088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>316</v>
       </c>
@@ -12120,7 +12120,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>317</v>
       </c>
@@ -12152,7 +12152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>318</v>
       </c>
@@ -12184,7 +12184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>319</v>
       </c>
@@ -12216,7 +12216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>320</v>
       </c>
@@ -12248,7 +12248,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>321</v>
       </c>
@@ -12280,7 +12280,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>322</v>
       </c>
@@ -12312,7 +12312,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>323</v>
       </c>
@@ -12344,7 +12344,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>324</v>
       </c>
@@ -12376,7 +12376,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>325</v>
       </c>
@@ -12408,7 +12408,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>326</v>
       </c>
@@ -12440,7 +12440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>327</v>
       </c>
@@ -12472,7 +12472,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>328</v>
       </c>
@@ -12504,7 +12504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>329</v>
       </c>
@@ -12536,7 +12536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>330</v>
       </c>
@@ -12568,7 +12568,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>331</v>
       </c>
@@ -12600,7 +12600,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>332</v>
       </c>
@@ -12632,7 +12632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>333</v>
       </c>
@@ -12664,7 +12664,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>334</v>
       </c>
@@ -12696,7 +12696,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>335</v>
       </c>
@@ -12728,7 +12728,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>336</v>
       </c>
@@ -12760,7 +12760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>337</v>
       </c>
@@ -12792,7 +12792,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>338</v>
       </c>
@@ -12824,7 +12824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>339</v>
       </c>
@@ -12856,7 +12856,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>340</v>
       </c>
@@ -12888,7 +12888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>341</v>
       </c>
@@ -12920,7 +12920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>342</v>
       </c>
@@ -12952,7 +12952,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>343</v>
       </c>
@@ -12984,7 +12984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>344</v>
       </c>
@@ -13016,7 +13016,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>345</v>
       </c>
@@ -13048,7 +13048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>346</v>
       </c>
@@ -13080,7 +13080,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>347</v>
       </c>
@@ -13112,7 +13112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>348</v>
       </c>
@@ -13144,7 +13144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>349</v>
       </c>
@@ -13176,7 +13176,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>350</v>
       </c>
@@ -13208,7 +13208,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>351</v>
       </c>
@@ -13240,7 +13240,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>352</v>
       </c>
@@ -13272,7 +13272,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>353</v>
       </c>
@@ -13304,7 +13304,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>354</v>
       </c>
@@ -13336,7 +13336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>355</v>
       </c>
@@ -13368,7 +13368,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>356</v>
       </c>
@@ -13400,7 +13400,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>357</v>
       </c>
@@ -13432,7 +13432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>358</v>
       </c>
@@ -13464,7 +13464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>359</v>
       </c>
@@ -13496,7 +13496,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>360</v>
       </c>
@@ -13528,7 +13528,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>361</v>
       </c>
@@ -13560,7 +13560,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>362</v>
       </c>
@@ -13592,7 +13592,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>363</v>
       </c>
@@ -13624,7 +13624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>364</v>
       </c>
@@ -13656,7 +13656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>365</v>
       </c>
@@ -13688,7 +13688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>366</v>
       </c>
@@ -13720,7 +13720,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>367</v>
       </c>
@@ -13752,7 +13752,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>368</v>
       </c>
@@ -13784,7 +13784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>369</v>
       </c>
@@ -13816,7 +13816,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>370</v>
       </c>
@@ -13848,7 +13848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>371</v>
       </c>
@@ -13880,7 +13880,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>372</v>
       </c>
@@ -13912,7 +13912,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>373</v>
       </c>
@@ -13944,7 +13944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>374</v>
       </c>
@@ -13976,7 +13976,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>375</v>
       </c>
@@ -14008,7 +14008,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>376</v>
       </c>
@@ -14040,7 +14040,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>377</v>
       </c>
@@ -14072,7 +14072,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>378</v>
       </c>
@@ -14104,7 +14104,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>379</v>
       </c>
@@ -14136,7 +14136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>380</v>
       </c>
@@ -14168,7 +14168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>381</v>
       </c>
@@ -14200,7 +14200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>382</v>
       </c>
@@ -14232,7 +14232,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>383</v>
       </c>
@@ -14264,7 +14264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>384</v>
       </c>
@@ -14296,7 +14296,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>385</v>
       </c>
@@ -14328,7 +14328,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>386</v>
       </c>
@@ -14360,7 +14360,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>387</v>
       </c>
@@ -14392,7 +14392,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>388</v>
       </c>
@@ -14424,7 +14424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>389</v>
       </c>
@@ -14456,7 +14456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>390</v>
       </c>
@@ -14488,7 +14488,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>391</v>
       </c>
@@ -14520,7 +14520,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>392</v>
       </c>
@@ -14552,7 +14552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>393</v>
       </c>
@@ -14584,7 +14584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>394</v>
       </c>
@@ -14616,7 +14616,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>395</v>
       </c>
@@ -14648,7 +14648,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>396</v>
       </c>
@@ -14680,7 +14680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>397</v>
       </c>
@@ -14712,7 +14712,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>398</v>
       </c>
@@ -14744,7 +14744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>399</v>
       </c>
@@ -14776,7 +14776,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>400</v>
       </c>
@@ -14808,7 +14808,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>401</v>
       </c>
@@ -14840,7 +14840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>402</v>
       </c>
@@ -14872,7 +14872,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>403</v>
       </c>
@@ -14904,7 +14904,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>404</v>
       </c>
@@ -14936,7 +14936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>405</v>
       </c>
@@ -14968,7 +14968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>406</v>
       </c>
@@ -15000,7 +15000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>407</v>
       </c>
@@ -15032,7 +15032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>408</v>
       </c>
@@ -15064,7 +15064,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>409</v>
       </c>
@@ -15096,7 +15096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>410</v>
       </c>
@@ -15128,7 +15128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>411</v>
       </c>
@@ -15160,7 +15160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>412</v>
       </c>
@@ -15192,7 +15192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>413</v>
       </c>
@@ -15224,7 +15224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>414</v>
       </c>
@@ -15256,7 +15256,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>415</v>
       </c>
@@ -15288,7 +15288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>416</v>
       </c>
@@ -15320,7 +15320,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>417</v>
       </c>
@@ -15352,7 +15352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>418</v>
       </c>
@@ -15384,7 +15384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>419</v>
       </c>
@@ -15416,7 +15416,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>420</v>
       </c>
@@ -15448,7 +15448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>421</v>
       </c>
@@ -15480,7 +15480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>422</v>
       </c>
@@ -15512,7 +15512,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>423</v>
       </c>
@@ -15544,7 +15544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>424</v>
       </c>
@@ -15576,7 +15576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>425</v>
       </c>
@@ -15608,7 +15608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>426</v>
       </c>
@@ -15640,7 +15640,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>427</v>
       </c>
@@ -15672,7 +15672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>428</v>
       </c>
@@ -15704,7 +15704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>429</v>
       </c>
@@ -15736,7 +15736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>430</v>
       </c>
@@ -15768,7 +15768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>431</v>
       </c>
@@ -15800,7 +15800,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>432</v>
       </c>
@@ -15832,7 +15832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>433</v>
       </c>
@@ -15864,7 +15864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>434</v>
       </c>
@@ -15896,7 +15896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>435</v>
       </c>
@@ -15928,7 +15928,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>436</v>
       </c>
@@ -15960,7 +15960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>437</v>
       </c>
@@ -15992,7 +15992,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>438</v>
       </c>
@@ -16024,7 +16024,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>439</v>
       </c>
@@ -16056,7 +16056,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>440</v>
       </c>
@@ -16088,7 +16088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>441</v>
       </c>
@@ -16120,7 +16120,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>442</v>
       </c>
@@ -16152,7 +16152,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>443</v>
       </c>
@@ -16184,7 +16184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>444</v>
       </c>
@@ -16216,7 +16216,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>445</v>
       </c>
@@ -16248,7 +16248,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>446</v>
       </c>
@@ -16280,7 +16280,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>447</v>
       </c>
@@ -16312,7 +16312,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>448</v>
       </c>
@@ -16344,7 +16344,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>449</v>
       </c>
@@ -16376,7 +16376,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>450</v>
       </c>
@@ -16408,7 +16408,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>451</v>
       </c>
@@ -16440,7 +16440,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>452</v>
       </c>
@@ -16472,7 +16472,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>453</v>
       </c>
@@ -16504,7 +16504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>454</v>
       </c>
@@ -16536,7 +16536,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>455</v>
       </c>
@@ -16568,7 +16568,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>456</v>
       </c>
@@ -16600,7 +16600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>457</v>
       </c>
@@ -16632,7 +16632,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>458</v>
       </c>
@@ -16664,7 +16664,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>459</v>
       </c>
@@ -16696,7 +16696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>460</v>
       </c>
@@ -16728,7 +16728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>461</v>
       </c>
@@ -16760,7 +16760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>462</v>
       </c>
@@ -16792,7 +16792,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>463</v>
       </c>
@@ -16824,7 +16824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>464</v>
       </c>
@@ -16856,7 +16856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>465</v>
       </c>
@@ -16888,7 +16888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>466</v>
       </c>
@@ -16920,7 +16920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>467</v>
       </c>
@@ -16952,7 +16952,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>468</v>
       </c>
@@ -16984,7 +16984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>469</v>
       </c>
@@ -17016,7 +17016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>470</v>
       </c>
@@ -17048,7 +17048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>471</v>
       </c>
@@ -17080,7 +17080,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>472</v>
       </c>
@@ -17112,7 +17112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>473</v>
       </c>
@@ -17144,7 +17144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>474</v>
       </c>
@@ -17176,7 +17176,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>475</v>
       </c>
@@ -17208,7 +17208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>476</v>
       </c>
@@ -17240,7 +17240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>477</v>
       </c>
@@ -17272,7 +17272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>478</v>
       </c>
@@ -17304,7 +17304,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>479</v>
       </c>
@@ -17336,7 +17336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>480</v>
       </c>
@@ -17368,7 +17368,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>481</v>
       </c>
@@ -17400,7 +17400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>482</v>
       </c>
@@ -17432,7 +17432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>483</v>
       </c>
@@ -17464,7 +17464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>484</v>
       </c>
@@ -17496,7 +17496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>485</v>
       </c>
@@ -17528,7 +17528,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>486</v>
       </c>
@@ -17560,7 +17560,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>487</v>
       </c>
@@ -17592,7 +17592,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>488</v>
       </c>
@@ -17624,7 +17624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>489</v>
       </c>
@@ -17656,7 +17656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>490</v>
       </c>
@@ -17688,7 +17688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>491</v>
       </c>
@@ -17720,7 +17720,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>492</v>
       </c>
@@ -17752,7 +17752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>493</v>
       </c>
@@ -17784,7 +17784,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>494</v>
       </c>
@@ -17816,7 +17816,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>495</v>
       </c>
@@ -17848,7 +17848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>496</v>
       </c>
@@ -17880,7 +17880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>497</v>
       </c>
@@ -17912,7 +17912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>498</v>
       </c>
@@ -17944,7 +17944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>499</v>
       </c>
@@ -17976,7 +17976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>500</v>
       </c>
@@ -18008,7 +18008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>501</v>
       </c>
@@ -18040,7 +18040,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>502</v>
       </c>
@@ -18072,7 +18072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>503</v>
       </c>
@@ -18104,7 +18104,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>504</v>
       </c>
@@ -18136,7 +18136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>505</v>
       </c>
@@ -18168,7 +18168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>506</v>
       </c>
@@ -18200,7 +18200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>507</v>
       </c>
@@ -18232,7 +18232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>508</v>
       </c>
@@ -18264,7 +18264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>509</v>
       </c>
@@ -18296,7 +18296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>510</v>
       </c>
@@ -18328,7 +18328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>511</v>
       </c>
@@ -18360,7 +18360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>512</v>
       </c>
@@ -18392,7 +18392,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>513</v>
       </c>
@@ -18424,7 +18424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>514</v>
       </c>
@@ -18456,7 +18456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>515</v>
       </c>
@@ -18488,7 +18488,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>516</v>
       </c>
@@ -18520,7 +18520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>517</v>
       </c>
@@ -18552,7 +18552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>518</v>
       </c>
@@ -18584,7 +18584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>519</v>
       </c>
@@ -18616,7 +18616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>520</v>
       </c>
@@ -18648,7 +18648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>521</v>
       </c>
@@ -18680,7 +18680,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>522</v>
       </c>
@@ -18712,7 +18712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>523</v>
       </c>
@@ -18744,7 +18744,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>524</v>
       </c>
@@ -18776,7 +18776,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>525</v>
       </c>
@@ -18808,7 +18808,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>526</v>
       </c>
@@ -18840,7 +18840,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>527</v>
       </c>
@@ -18872,7 +18872,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>528</v>
       </c>
@@ -18904,7 +18904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>529</v>
       </c>
@@ -18936,7 +18936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>530</v>
       </c>
@@ -18968,7 +18968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>531</v>
       </c>
@@ -19000,7 +19000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>532</v>
       </c>
@@ -19032,7 +19032,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>533</v>
       </c>
@@ -19064,7 +19064,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>534</v>
       </c>
@@ -19096,7 +19096,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>535</v>
       </c>
@@ -19128,7 +19128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>536</v>
       </c>
@@ -19160,7 +19160,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>537</v>
       </c>
@@ -19192,7 +19192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>538</v>
       </c>
@@ -19224,7 +19224,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>539</v>
       </c>
@@ -19256,7 +19256,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>540</v>
       </c>
@@ -19288,7 +19288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>541</v>
       </c>
@@ -19320,7 +19320,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>542</v>
       </c>
@@ -19352,7 +19352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>543</v>
       </c>
@@ -19384,7 +19384,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>544</v>
       </c>
@@ -19416,7 +19416,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>545</v>
       </c>
@@ -19448,7 +19448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>546</v>
       </c>
@@ -19480,7 +19480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="497" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>547</v>
       </c>
@@ -19512,7 +19512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="498" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>548</v>
       </c>
@@ -19544,7 +19544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>549</v>
       </c>
@@ -19576,7 +19576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="500" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>550</v>
       </c>
@@ -19608,7 +19608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="501" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>551</v>
       </c>
@@ -19640,7 +19640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>552</v>
       </c>
@@ -19672,7 +19672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="503" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>553</v>
       </c>
@@ -19704,7 +19704,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="504" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>554</v>
       </c>
@@ -19736,7 +19736,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="505" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>555</v>
       </c>
@@ -19768,7 +19768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="506" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>556</v>
       </c>
@@ -19800,7 +19800,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="507" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>557</v>
       </c>
@@ -19832,7 +19832,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="508" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>558</v>
       </c>
@@ -19864,7 +19864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="509" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>559</v>
       </c>
@@ -19896,7 +19896,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="510" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>560</v>
       </c>
@@ -19928,7 +19928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="511" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>561</v>
       </c>
@@ -19960,7 +19960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="512" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>562</v>
       </c>
@@ -19992,7 +19992,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="513" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>563</v>
       </c>
@@ -20024,7 +20024,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="514" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>564</v>
       </c>
@@ -20056,7 +20056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="515" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>565</v>
       </c>
@@ -20088,7 +20088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="516" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>566</v>
       </c>
@@ -20120,7 +20120,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="517" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>567</v>
       </c>
@@ -20152,7 +20152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="518" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>568</v>
       </c>
@@ -20184,7 +20184,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="519" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>569</v>
       </c>
@@ -20216,7 +20216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="520" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>570</v>
       </c>
@@ -20248,7 +20248,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="521" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>571</v>
       </c>
@@ -20280,7 +20280,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="522" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>572</v>
       </c>
@@ -20312,7 +20312,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="523" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>573</v>
       </c>
@@ -20344,7 +20344,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="524" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>574</v>
       </c>
@@ -20376,7 +20376,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="525" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>575</v>
       </c>
@@ -20408,7 +20408,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="526" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>576</v>
       </c>
@@ -20440,7 +20440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="527" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>577</v>
       </c>
@@ -20472,7 +20472,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="528" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>578</v>
       </c>
@@ -20504,7 +20504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="529" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>579</v>
       </c>
@@ -20536,7 +20536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="530" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>580</v>
       </c>
@@ -20568,7 +20568,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="531" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>581</v>
       </c>
@@ -20600,7 +20600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="532" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>582</v>
       </c>
@@ -20632,7 +20632,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="533" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>583</v>
       </c>
@@ -20664,7 +20664,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="534" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>584</v>
       </c>
@@ -20696,7 +20696,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="535" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>585</v>
       </c>
@@ -20728,7 +20728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="536" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>586</v>
       </c>
@@ -20760,7 +20760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="537" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>587</v>
       </c>
@@ -20792,7 +20792,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="538" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>588</v>
       </c>
@@ -20824,7 +20824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="539" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>589</v>
       </c>
@@ -20856,7 +20856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="540" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>590</v>
       </c>
@@ -20888,7 +20888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="541" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>591</v>
       </c>
@@ -20920,7 +20920,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="542" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>592</v>
       </c>
@@ -20952,7 +20952,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="543" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>593</v>
       </c>
@@ -20984,7 +20984,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="544" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>594</v>
       </c>
@@ -21016,7 +21016,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="545" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>595</v>
       </c>
@@ -21048,7 +21048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="546" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>596</v>
       </c>
@@ -21080,7 +21080,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="547" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>597</v>
       </c>
@@ -21112,7 +21112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="548" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>598</v>
       </c>
@@ -21144,7 +21144,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="549" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>599</v>
       </c>
@@ -21176,7 +21176,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="550" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>600</v>
       </c>
@@ -21208,7 +21208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="551" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>601</v>
       </c>
@@ -21240,7 +21240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="552" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>602</v>
       </c>
@@ -21272,7 +21272,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="553" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>603</v>
       </c>
@@ -21304,7 +21304,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="554" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>604</v>
       </c>
@@ -21336,7 +21336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="555" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>605</v>
       </c>
@@ -21368,7 +21368,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="556" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>606</v>
       </c>
@@ -21400,7 +21400,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="557" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>607</v>
       </c>
@@ -21432,7 +21432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="558" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>608</v>
       </c>
@@ -21464,7 +21464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="559" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>609</v>
       </c>
@@ -21496,7 +21496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="560" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>610</v>
       </c>
@@ -21528,7 +21528,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="561" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>611</v>
       </c>
@@ -21560,7 +21560,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="562" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>612</v>
       </c>
@@ -21592,7 +21592,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="563" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>613</v>
       </c>
@@ -21624,7 +21624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="564" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>614</v>
       </c>
@@ -21656,7 +21656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="565" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>615</v>
       </c>
@@ -21688,7 +21688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="566" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>616</v>
       </c>
@@ -21720,7 +21720,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="567" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>617</v>
       </c>
@@ -21752,7 +21752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="568" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>618</v>
       </c>
@@ -21784,7 +21784,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="569" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>619</v>
       </c>
@@ -21816,7 +21816,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="570" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>620</v>
       </c>
@@ -21848,7 +21848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="571" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>621</v>
       </c>
@@ -21880,7 +21880,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="572" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>622</v>
       </c>
@@ -21912,7 +21912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="573" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>623</v>
       </c>
@@ -21944,7 +21944,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="574" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>624</v>
       </c>
@@ -21976,7 +21976,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="575" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>625</v>
       </c>
@@ -22008,7 +22008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="576" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>626</v>
       </c>
@@ -22040,7 +22040,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="577" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>627</v>
       </c>
@@ -22072,7 +22072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="578" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>628</v>
       </c>
@@ -22104,7 +22104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="579" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>629</v>
       </c>
@@ -22136,7 +22136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="580" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>630</v>
       </c>
@@ -22168,7 +22168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="581" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>631</v>
       </c>
@@ -22200,7 +22200,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="582" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>632</v>
       </c>
@@ -22232,7 +22232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="583" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>633</v>
       </c>
@@ -22264,7 +22264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="584" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>634</v>
       </c>
@@ -22296,7 +22296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="585" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>635</v>
       </c>
@@ -22328,7 +22328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="586" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>636</v>
       </c>
@@ -22360,7 +22360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="587" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>637</v>
       </c>
@@ -22392,7 +22392,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="588" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>638</v>
       </c>
@@ -22424,7 +22424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="589" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>639</v>
       </c>
@@ -22456,7 +22456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="590" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>640</v>
       </c>
@@ -22488,7 +22488,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="591" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>641</v>
       </c>
@@ -22520,7 +22520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="592" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>642</v>
       </c>
@@ -22552,7 +22552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="593" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>643</v>
       </c>
@@ -22584,7 +22584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="594" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>644</v>
       </c>
@@ -22616,7 +22616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="595" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>645</v>
       </c>
@@ -22648,7 +22648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="596" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>646</v>
       </c>
@@ -22680,7 +22680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="597" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>647</v>
       </c>
@@ -22712,7 +22712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="598" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>648</v>
       </c>
@@ -22744,7 +22744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="599" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>649</v>
       </c>
@@ -22776,7 +22776,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="600" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>650</v>
       </c>
@@ -22808,7 +22808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="601" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>651</v>
       </c>
@@ -22840,7 +22840,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="602" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>652</v>
       </c>
@@ -22872,7 +22872,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="603" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>653</v>
       </c>
@@ -22904,7 +22904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="604" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>654</v>
       </c>
@@ -22936,7 +22936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="605" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>655</v>
       </c>
@@ -22968,7 +22968,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="606" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>656</v>
       </c>
@@ -23000,7 +23000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="607" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>657</v>
       </c>
@@ -23032,7 +23032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="608" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>658</v>
       </c>
@@ -23064,7 +23064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="609" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>659</v>
       </c>
@@ -23096,7 +23096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="610" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>660</v>
       </c>
@@ -23128,7 +23128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="611" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>661</v>
       </c>
@@ -23160,7 +23160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="612" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>662</v>
       </c>
@@ -23192,7 +23192,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="613" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>663</v>
       </c>
@@ -23224,7 +23224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="614" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>664</v>
       </c>
@@ -23256,7 +23256,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="615" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>665</v>
       </c>
@@ -23288,7 +23288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="616" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>666</v>
       </c>
@@ -23320,7 +23320,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="617" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>667</v>
       </c>
@@ -23352,7 +23352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="618" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>668</v>
       </c>
@@ -23384,7 +23384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="619" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>669</v>
       </c>
@@ -23416,7 +23416,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="620" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>670</v>
       </c>
@@ -23448,7 +23448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="621" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>671</v>
       </c>
@@ -23480,7 +23480,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="622" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>672</v>
       </c>
@@ -23512,7 +23512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="623" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>673</v>
       </c>
@@ -23544,7 +23544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="624" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>674</v>
       </c>
@@ -23576,7 +23576,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="625" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>675</v>
       </c>
@@ -23608,7 +23608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="626" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>676</v>
       </c>
@@ -23640,7 +23640,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="627" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>677</v>
       </c>
@@ -23672,7 +23672,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="628" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>678</v>
       </c>
@@ -23704,7 +23704,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="629" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>679</v>
       </c>
@@ -23736,7 +23736,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="630" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>680</v>
       </c>
@@ -23768,7 +23768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="631" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>681</v>
       </c>
@@ -23800,7 +23800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="632" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>682</v>
       </c>
@@ -23832,7 +23832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="633" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>683</v>
       </c>
@@ -23864,7 +23864,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="634" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>684</v>
       </c>
@@ -23896,7 +23896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="635" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>685</v>
       </c>
@@ -23928,7 +23928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="636" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>686</v>
       </c>
@@ -23960,7 +23960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="637" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>687</v>
       </c>
@@ -23992,7 +23992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="638" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>688</v>
       </c>
@@ -24024,7 +24024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="639" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>689</v>
       </c>
@@ -24056,7 +24056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="640" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>690</v>
       </c>
@@ -24088,7 +24088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="641" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>691</v>
       </c>
@@ -24120,7 +24120,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="642" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>692</v>
       </c>
@@ -24152,7 +24152,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="643" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>693</v>
       </c>
@@ -24184,7 +24184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="644" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>694</v>
       </c>
@@ -24216,7 +24216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="645" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>695</v>
       </c>
@@ -24248,7 +24248,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="646" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>696</v>
       </c>
@@ -24280,7 +24280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="647" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>697</v>
       </c>
@@ -24312,7 +24312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="648" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>698</v>
       </c>
@@ -24344,7 +24344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="649" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>699</v>
       </c>
@@ -24376,7 +24376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="650" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>700</v>
       </c>
@@ -24408,7 +24408,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="651" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>701</v>
       </c>
@@ -24440,7 +24440,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="652" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>702</v>
       </c>
@@ -24472,7 +24472,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="653" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>703</v>
       </c>
@@ -24504,7 +24504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="654" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>704</v>
       </c>
@@ -24536,7 +24536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="655" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>705</v>
       </c>
@@ -24568,7 +24568,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="656" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>706</v>
       </c>
@@ -24600,7 +24600,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="657" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>707</v>
       </c>
@@ -24632,7 +24632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="658" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>708</v>
       </c>
@@ -24664,7 +24664,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="659" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>709</v>
       </c>
@@ -24696,7 +24696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="660" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>710</v>
       </c>
@@ -24728,7 +24728,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="661" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>711</v>
       </c>
@@ -24760,7 +24760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="662" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>712</v>
       </c>
@@ -24792,7 +24792,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="663" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>713</v>
       </c>
@@ -24824,7 +24824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="664" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>714</v>
       </c>
@@ -24856,7 +24856,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="665" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>715</v>
       </c>
@@ -24888,7 +24888,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="666" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>716</v>
       </c>
@@ -24920,7 +24920,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="667" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
         <v>717</v>
       </c>
@@ -24952,7 +24952,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="668" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>718</v>
       </c>
@@ -24984,7 +24984,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="669" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>719</v>
       </c>
@@ -25016,7 +25016,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="670" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>720</v>
       </c>
@@ -25048,7 +25048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="671" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>721</v>
       </c>
@@ -25080,7 +25080,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="672" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>722</v>
       </c>
@@ -25112,7 +25112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="673" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>723</v>
       </c>
@@ -25144,7 +25144,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="674" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>724</v>
       </c>
@@ -25176,7 +25176,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="675" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>725</v>
       </c>
@@ -25208,7 +25208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="676" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>726</v>
       </c>
@@ -25240,7 +25240,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="677" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>727</v>
       </c>
@@ -25272,7 +25272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="678" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>728</v>
       </c>
@@ -25304,7 +25304,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="679" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>729</v>
       </c>
@@ -25336,7 +25336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="680" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>730</v>
       </c>
@@ -25368,7 +25368,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="681" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
         <v>731</v>
       </c>
@@ -25400,7 +25400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="682" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>732</v>
       </c>
@@ -25432,7 +25432,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="683" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>733</v>
       </c>
@@ -25464,7 +25464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="684" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>734</v>
       </c>
@@ -25496,7 +25496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="685" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>735</v>
       </c>
@@ -25528,7 +25528,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="686" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>736</v>
       </c>
@@ -25560,7 +25560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="687" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>737</v>
       </c>
@@ -25592,7 +25592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="688" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
         <v>738</v>
       </c>
@@ -25624,7 +25624,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="689" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
         <v>739</v>
       </c>
@@ -25656,7 +25656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="690" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
         <v>740</v>
       </c>
@@ -25688,7 +25688,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="691" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
         <v>741</v>
       </c>
@@ -25720,7 +25720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="692" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
         <v>742</v>
       </c>
@@ -25752,7 +25752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="693" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
         <v>743</v>
       </c>
@@ -25784,7 +25784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="694" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
         <v>744</v>
       </c>
@@ -25816,7 +25816,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="695" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
         <v>745</v>
       </c>
@@ -25848,7 +25848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="696" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
         <v>746</v>
       </c>
@@ -25880,7 +25880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="697" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
         <v>747</v>
       </c>
@@ -25912,7 +25912,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="698" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
         <v>748</v>
       </c>
@@ -25944,7 +25944,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="699" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
         <v>749</v>
       </c>
@@ -25976,7 +25976,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="700" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
         <v>750</v>
       </c>
@@ -26008,7 +26008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="701" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
         <v>751</v>
       </c>
@@ -26040,7 +26040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="702" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
         <v>752</v>
       </c>
@@ -26072,7 +26072,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="703" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
         <v>753</v>
       </c>
@@ -26104,7 +26104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="704" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
         <v>754</v>
       </c>
@@ -26136,7 +26136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="705" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
         <v>755</v>
       </c>
@@ -26168,7 +26168,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="706" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
         <v>756</v>
       </c>
@@ -26200,7 +26200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="707" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
         <v>757</v>
       </c>
@@ -26232,7 +26232,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="708" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
         <v>758</v>
       </c>
@@ -26264,7 +26264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="709" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
         <v>759</v>
       </c>
@@ -26296,7 +26296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="710" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
         <v>760</v>
       </c>
@@ -26328,7 +26328,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="711" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
         <v>761</v>
       </c>
@@ -26360,7 +26360,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="712" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
         <v>762</v>
       </c>
@@ -26392,7 +26392,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="713" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
         <v>763</v>
       </c>
@@ -26424,7 +26424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="714" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
         <v>764</v>
       </c>
@@ -26456,7 +26456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="715" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
         <v>765</v>
       </c>
@@ -26488,7 +26488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="716" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
         <v>766</v>
       </c>
@@ -26520,7 +26520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="717" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
         <v>767</v>
       </c>
@@ -26552,7 +26552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="718" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
         <v>768</v>
       </c>
@@ -26584,7 +26584,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="719" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
         <v>769</v>
       </c>
@@ -26616,7 +26616,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="720" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
         <v>770</v>
       </c>
@@ -26648,7 +26648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="721" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
         <v>771</v>
       </c>
@@ -26680,7 +26680,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="722" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>772</v>
       </c>
@@ -26712,7 +26712,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="723" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>773</v>
       </c>
@@ -26744,7 +26744,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="724" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
         <v>774</v>
       </c>
@@ -26776,7 +26776,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="725" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>775</v>
       </c>
@@ -26808,7 +26808,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="726" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
         <v>776</v>
       </c>
@@ -26840,7 +26840,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="727" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
         <v>777</v>
       </c>
@@ -26872,7 +26872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="728" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
         <v>778</v>
       </c>
@@ -26904,7 +26904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="729" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
         <v>779</v>
       </c>
@@ -26936,7 +26936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="730" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
         <v>780</v>
       </c>
@@ -26968,7 +26968,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="731" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
         <v>781</v>
       </c>
@@ -27000,7 +27000,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="732" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
         <v>782</v>
       </c>
@@ -27032,7 +27032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="733" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
         <v>783</v>
       </c>
@@ -27064,7 +27064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="734" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
         <v>784</v>
       </c>
@@ -27096,7 +27096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="735" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>785</v>
       </c>
@@ -27128,7 +27128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="736" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>786</v>
       </c>
@@ -27160,7 +27160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="737" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
         <v>787</v>
       </c>
@@ -27192,7 +27192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="738" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
         <v>788</v>
       </c>
@@ -27224,7 +27224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="739" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
         <v>789</v>
       </c>
@@ -27256,7 +27256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="740" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
         <v>790</v>
       </c>
@@ -27288,7 +27288,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="741" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
         <v>791</v>
       </c>
@@ -27320,7 +27320,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="742" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
         <v>792</v>
       </c>
@@ -27352,7 +27352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="743" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
         <v>793</v>
       </c>
@@ -27384,7 +27384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="744" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
         <v>794</v>
       </c>
@@ -27416,7 +27416,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="745" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
         <v>795</v>
       </c>
@@ -27448,7 +27448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="746" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
         <v>796</v>
       </c>
@@ -27480,7 +27480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="747" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
         <v>797</v>
       </c>
@@ -27512,7 +27512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="748" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
         <v>798</v>
       </c>
@@ -27544,7 +27544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="749" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
         <v>799</v>
       </c>
@@ -27576,7 +27576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="750" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
         <v>800</v>
       </c>
@@ -27608,7 +27608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="751" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
         <v>801</v>
       </c>
@@ -27640,7 +27640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="752" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
         <v>802</v>
       </c>
@@ -27672,7 +27672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="753" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
         <v>803</v>
       </c>
@@ -27704,7 +27704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="754" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
         <v>804</v>
       </c>
@@ -27736,7 +27736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="755" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
         <v>805</v>
       </c>
@@ -27768,7 +27768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="756" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
         <v>806</v>
       </c>
@@ -27800,7 +27800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="757" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
         <v>807</v>
       </c>
@@ -27832,7 +27832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="758" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
         <v>808</v>
       </c>
@@ -27864,7 +27864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="759" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
         <v>809</v>
       </c>
@@ -27896,7 +27896,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="760" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
         <v>810</v>
       </c>
@@ -27928,7 +27928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="761" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
         <v>811</v>
       </c>
@@ -27960,7 +27960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="762" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
         <v>812</v>
       </c>
@@ -27992,7 +27992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="763" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
         <v>813</v>
       </c>
@@ -28024,7 +28024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="764" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
         <v>814</v>
       </c>
@@ -28056,7 +28056,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="765" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
         <v>815</v>
       </c>
@@ -28088,7 +28088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="766" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
         <v>816</v>
       </c>
@@ -28120,7 +28120,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="767" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
         <v>817</v>
       </c>
@@ -28152,7 +28152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="768" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
         <v>818</v>
       </c>
@@ -28184,7 +28184,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="769" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
         <v>819</v>
       </c>
@@ -28216,7 +28216,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="770" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
         <v>820</v>
       </c>
@@ -28248,7 +28248,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="771" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
         <v>821</v>
       </c>
@@ -28280,7 +28280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="772" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
         <v>822</v>
       </c>
@@ -28312,7 +28312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="773" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
         <v>823</v>
       </c>
@@ -28344,7 +28344,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="774" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A774" t="s">
         <v>824</v>
       </c>
@@ -28376,7 +28376,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="775" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
         <v>825</v>
       </c>
@@ -28408,7 +28408,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="776" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
         <v>826</v>
       </c>
@@ -28440,7 +28440,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="777" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A777" t="s">
         <v>827</v>
       </c>
@@ -28472,7 +28472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="778" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
         <v>828</v>
       </c>
@@ -28504,7 +28504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="779" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A779" t="s">
         <v>829</v>
       </c>
@@ -28536,7 +28536,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="780" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A780" t="s">
         <v>830</v>
       </c>
@@ -28568,7 +28568,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="781" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
         <v>831</v>
       </c>
@@ -28600,7 +28600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="782" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
         <v>832</v>
       </c>
@@ -28632,7 +28632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="783" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
         <v>833</v>
       </c>
@@ -28664,7 +28664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="784" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
         <v>834</v>
       </c>
@@ -28696,7 +28696,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="785" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
         <v>835</v>
       </c>
@@ -28728,7 +28728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="786" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
         <v>836</v>
       </c>
@@ -28760,7 +28760,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="787" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
         <v>837</v>
       </c>
@@ -28792,7 +28792,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="788" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A788" t="s">
         <v>838</v>
       </c>
@@ -28824,7 +28824,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="789" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A789" t="s">
         <v>839</v>
       </c>
@@ -28856,7 +28856,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="790" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
         <v>840</v>
       </c>
@@ -28888,7 +28888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="791" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
         <v>841</v>
       </c>
@@ -28920,7 +28920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="792" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A792" t="s">
         <v>842</v>
       </c>
@@ -28952,7 +28952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="793" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A793" t="s">
         <v>843</v>
       </c>
@@ -28984,7 +28984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="794" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
         <v>844</v>
       </c>
@@ -29016,7 +29016,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="795" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A795" t="s">
         <v>845</v>
       </c>
@@ -29048,7 +29048,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="796" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A796" t="s">
         <v>846</v>
       </c>
@@ -29080,7 +29080,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="797" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A797" t="s">
         <v>847</v>
       </c>
@@ -29112,7 +29112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="798" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A798" t="s">
         <v>848</v>
       </c>
@@ -29144,7 +29144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="799" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A799" t="s">
         <v>849</v>
       </c>
@@ -29176,7 +29176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="800" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A800" t="s">
         <v>850</v>
       </c>
@@ -29208,7 +29208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="801" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A801" t="s">
         <v>851</v>
       </c>
@@ -29240,7 +29240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="802" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
         <v>852</v>
       </c>
@@ -29272,7 +29272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="803" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A803" t="s">
         <v>853</v>
       </c>
@@ -29304,7 +29304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="804" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A804" t="s">
         <v>854</v>
       </c>
@@ -29336,7 +29336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="805" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
         <v>855</v>
       </c>
@@ -29368,7 +29368,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="806" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A806" t="s">
         <v>856</v>
       </c>
@@ -29400,7 +29400,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="807" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A807" t="s">
         <v>857</v>
       </c>
@@ -29432,7 +29432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="808" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A808" t="s">
         <v>858</v>
       </c>
@@ -29464,7 +29464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="809" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A809" t="s">
         <v>859</v>
       </c>
@@ -29496,7 +29496,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="810" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A810" t="s">
         <v>860</v>
       </c>
@@ -29528,7 +29528,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="811" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
         <v>861</v>
       </c>
@@ -29560,7 +29560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="812" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
         <v>862</v>
       </c>
@@ -29592,7 +29592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="813" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
         <v>863</v>
       </c>
@@ -29624,7 +29624,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="814" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A814" t="s">
         <v>864</v>
       </c>
@@ -29656,7 +29656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="815" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A815" t="s">
         <v>865</v>
       </c>
@@ -29688,7 +29688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="816" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
         <v>866</v>
       </c>
@@ -29720,7 +29720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="817" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
         <v>867</v>
       </c>
@@ -29752,7 +29752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="818" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
         <v>868</v>
       </c>
@@ -29784,7 +29784,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="819" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
         <v>869</v>
       </c>
@@ -29816,7 +29816,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="820" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
         <v>870</v>
       </c>
@@ -29848,7 +29848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="821" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
         <v>871</v>
       </c>
@@ -29880,7 +29880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="822" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
         <v>872</v>
       </c>
@@ -29912,7 +29912,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="823" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
         <v>873</v>
       </c>
@@ -29944,7 +29944,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="824" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
         <v>874</v>
       </c>
@@ -29976,7 +29976,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="825" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
         <v>875</v>
       </c>
@@ -30008,7 +30008,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="826" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
         <v>876</v>
       </c>
@@ -30040,7 +30040,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="827" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
         <v>877</v>
       </c>
@@ -30072,7 +30072,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="828" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
         <v>878</v>
       </c>
@@ -30104,7 +30104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="829" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
         <v>879</v>
       </c>
@@ -30136,7 +30136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="830" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
         <v>880</v>
       </c>
@@ -30168,7 +30168,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="831" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
         <v>881</v>
       </c>
@@ -30200,7 +30200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="832" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
         <v>882</v>
       </c>
@@ -30232,7 +30232,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="833" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A833" t="s">
         <v>883</v>
       </c>
@@ -30264,7 +30264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="834" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A834" t="s">
         <v>884</v>
       </c>
@@ -30296,7 +30296,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="835" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A835" t="s">
         <v>885</v>
       </c>
@@ -30328,7 +30328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="836" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A836" t="s">
         <v>886</v>
       </c>
@@ -30360,7 +30360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="837" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A837" t="s">
         <v>887</v>
       </c>
@@ -30392,7 +30392,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="838" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A838" t="s">
         <v>888</v>
       </c>
@@ -30424,7 +30424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="839" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A839" t="s">
         <v>889</v>
       </c>
@@ -30456,7 +30456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="840" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A840" t="s">
         <v>890</v>
       </c>
@@ -30488,7 +30488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="841" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A841" t="s">
         <v>891</v>
       </c>
@@ -30520,7 +30520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="842" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A842" t="s">
         <v>892</v>
       </c>
@@ -30552,7 +30552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="843" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A843" t="s">
         <v>893</v>
       </c>
@@ -30584,7 +30584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="844" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A844" t="s">
         <v>894</v>
       </c>
@@ -30616,7 +30616,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="845" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A845" t="s">
         <v>895</v>
       </c>
@@ -30648,7 +30648,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="846" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A846" t="s">
         <v>896</v>
       </c>
@@ -30680,7 +30680,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="847" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A847" t="s">
         <v>897</v>
       </c>
@@ -30712,7 +30712,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="848" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A848" t="s">
         <v>898</v>
       </c>
@@ -30744,7 +30744,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="849" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A849" t="s">
         <v>899</v>
       </c>
@@ -30776,7 +30776,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="850" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A850" t="s">
         <v>900</v>
       </c>
@@ -30808,7 +30808,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="851" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A851" t="s">
         <v>901</v>
       </c>
@@ -30840,7 +30840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="852" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A852" t="s">
         <v>902</v>
       </c>
@@ -30872,7 +30872,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="853" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A853" t="s">
         <v>903</v>
       </c>
@@ -30904,7 +30904,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="854" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A854" t="s">
         <v>904</v>
       </c>
@@ -30936,7 +30936,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="855" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A855" t="s">
         <v>905</v>
       </c>
@@ -30968,7 +30968,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="856" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A856" t="s">
         <v>906</v>
       </c>
@@ -31000,7 +31000,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="857" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A857" t="s">
         <v>907</v>
       </c>
@@ -31032,7 +31032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="858" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A858" t="s">
         <v>908</v>
       </c>
@@ -31064,7 +31064,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="859" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A859" t="s">
         <v>909</v>
       </c>
@@ -31096,7 +31096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="860" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A860" t="s">
         <v>910</v>
       </c>
@@ -31128,7 +31128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="861" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="861" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A861" t="s">
         <v>911</v>
       </c>
@@ -31160,7 +31160,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="862" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="862" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A862" t="s">
         <v>912</v>
       </c>
@@ -31192,7 +31192,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="863" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="863" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A863" t="s">
         <v>913</v>
       </c>
@@ -31224,7 +31224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="864" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A864" t="s">
         <v>914</v>
       </c>
@@ -31256,7 +31256,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="865" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="865" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A865" t="s">
         <v>915</v>
       </c>
@@ -31288,7 +31288,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="866" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="866" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A866" t="s">
         <v>916</v>
       </c>
@@ -31320,7 +31320,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="867" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="867" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A867" t="s">
         <v>917</v>
       </c>
@@ -31352,7 +31352,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="868" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="868" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A868" t="s">
         <v>918</v>
       </c>
@@ -31384,7 +31384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="869" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="869" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A869" t="s">
         <v>919</v>
       </c>
@@ -31416,7 +31416,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="870" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="870" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A870" t="s">
         <v>920</v>
       </c>
@@ -31448,7 +31448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="871" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="871" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A871" t="s">
         <v>921</v>
       </c>
@@ -31480,7 +31480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="872" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="872" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A872" t="s">
         <v>922</v>
       </c>
@@ -31512,7 +31512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="873" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="873" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A873" t="s">
         <v>923</v>
       </c>
@@ -31544,7 +31544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="874" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="874" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A874" t="s">
         <v>924</v>
       </c>
@@ -31576,7 +31576,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="875" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="875" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A875" t="s">
         <v>925</v>
       </c>
@@ -31608,7 +31608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="876" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="876" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A876" t="s">
         <v>926</v>
       </c>
@@ -31640,7 +31640,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="877" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="877" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A877" t="s">
         <v>927</v>
       </c>
@@ -31672,7 +31672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="878" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="878" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A878" t="s">
         <v>928</v>
       </c>
@@ -31704,7 +31704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="879" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="879" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A879" t="s">
         <v>929</v>
       </c>
@@ -31736,7 +31736,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="880" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="880" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A880" t="s">
         <v>930</v>
       </c>
@@ -31768,7 +31768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="881" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="881" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A881" t="s">
         <v>931</v>
       </c>
@@ -31800,7 +31800,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="882" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="882" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A882" t="s">
         <v>932</v>
       </c>
@@ -31832,7 +31832,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="883" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="883" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A883" t="s">
         <v>933</v>
       </c>
@@ -31864,7 +31864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="884" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="884" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A884" t="s">
         <v>934</v>
       </c>
@@ -31896,7 +31896,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="885" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="885" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A885" t="s">
         <v>935</v>
       </c>
@@ -31928,7 +31928,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="886" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A886" t="s">
         <v>936</v>
       </c>
@@ -31960,7 +31960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="887" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A887" t="s">
         <v>937</v>
       </c>
@@ -31992,7 +31992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="888" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A888" t="s">
         <v>938</v>
       </c>
@@ -32024,7 +32024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="889" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A889" t="s">
         <v>939</v>
       </c>
@@ -32056,7 +32056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="890" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A890" t="s">
         <v>940</v>
       </c>
@@ -32088,7 +32088,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="891" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A891" t="s">
         <v>941</v>
       </c>
@@ -32120,7 +32120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="892" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A892" t="s">
         <v>942</v>
       </c>
@@ -32152,7 +32152,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="893" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A893" t="s">
         <v>943</v>
       </c>
@@ -32184,7 +32184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="894" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A894" t="s">
         <v>944</v>
       </c>
@@ -32216,7 +32216,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="895" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A895" t="s">
         <v>945</v>
       </c>
@@ -32248,7 +32248,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="896" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A896" t="s">
         <v>946</v>
       </c>
@@ -32280,7 +32280,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="897" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A897" t="s">
         <v>947</v>
       </c>
@@ -32312,7 +32312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="898" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A898" t="s">
         <v>948</v>
       </c>
@@ -32344,7 +32344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="899" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A899" t="s">
         <v>949</v>
       </c>
@@ -32376,7 +32376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="900" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A900" t="s">
         <v>950</v>
       </c>
@@ -32408,7 +32408,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="901" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A901" t="s">
         <v>951</v>
       </c>
@@ -32440,7 +32440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="902" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A902" t="s">
         <v>952</v>
       </c>
@@ -32472,7 +32472,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="903" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A903" t="s">
         <v>953</v>
       </c>
@@ -32504,7 +32504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="904" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A904" t="s">
         <v>954</v>
       </c>
@@ -32536,7 +32536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="905" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A905" t="s">
         <v>955</v>
       </c>
@@ -32568,7 +32568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="906" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A906" t="s">
         <v>956</v>
       </c>
@@ -32600,7 +32600,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="907" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="907" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A907" t="s">
         <v>957</v>
       </c>
@@ -32632,7 +32632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="908" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="908" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A908" t="s">
         <v>958</v>
       </c>
@@ -32664,7 +32664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="909" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="909" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A909" t="s">
         <v>959</v>
       </c>
@@ -32696,7 +32696,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="910" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="910" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A910" t="s">
         <v>960</v>
       </c>
@@ -32728,7 +32728,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="911" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="911" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A911" t="s">
         <v>961</v>
       </c>
@@ -32760,7 +32760,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="912" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="912" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A912" t="s">
         <v>962</v>
       </c>
@@ -32792,7 +32792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="913" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="913" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A913" t="s">
         <v>963</v>
       </c>
@@ -32824,7 +32824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="914" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="914" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A914" t="s">
         <v>964</v>
       </c>
@@ -32856,7 +32856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="915" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="915" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A915" t="s">
         <v>965</v>
       </c>
@@ -32888,7 +32888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="916" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="916" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A916" t="s">
         <v>966</v>
       </c>
@@ -32920,7 +32920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="917" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="917" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A917" t="s">
         <v>967</v>
       </c>
@@ -32952,7 +32952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="918" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="918" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A918" t="s">
         <v>968</v>
       </c>
@@ -32984,7 +32984,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="919" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="919" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A919" t="s">
         <v>969</v>
       </c>
@@ -33016,7 +33016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="920" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="920" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A920" t="s">
         <v>970</v>
       </c>
@@ -33048,7 +33048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="921" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="921" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A921" t="s">
         <v>971</v>
       </c>
@@ -33080,7 +33080,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="922" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="922" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A922" t="s">
         <v>972</v>
       </c>
@@ -33112,7 +33112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="923" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="923" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A923" t="s">
         <v>973</v>
       </c>
@@ -33144,7 +33144,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="924" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="924" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A924" t="s">
         <v>974</v>
       </c>
@@ -33176,7 +33176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="925" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="925" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A925" t="s">
         <v>975</v>
       </c>
@@ -33208,7 +33208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="926" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="926" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A926" t="s">
         <v>976</v>
       </c>
@@ -33240,7 +33240,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="927" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="927" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A927" t="s">
         <v>977</v>
       </c>
@@ -33272,7 +33272,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="928" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="928" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A928" t="s">
         <v>978</v>
       </c>
@@ -33304,7 +33304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="929" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="929" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A929" t="s">
         <v>979</v>
       </c>
@@ -33336,7 +33336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="930" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="930" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A930" t="s">
         <v>980</v>
       </c>
@@ -33368,7 +33368,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="931" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="931" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A931" t="s">
         <v>981</v>
       </c>
@@ -33400,7 +33400,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="932" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="932" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A932" t="s">
         <v>982</v>
       </c>
@@ -33432,7 +33432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="933" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="933" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A933" t="s">
         <v>983</v>
       </c>
@@ -33464,7 +33464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="934" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="934" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A934" t="s">
         <v>984</v>
       </c>
@@ -33496,7 +33496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="935" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="935" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A935" t="s">
         <v>985</v>
       </c>
@@ -33528,7 +33528,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="936" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="936" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A936" t="s">
         <v>986</v>
       </c>
@@ -33560,7 +33560,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="937" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="937" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A937" t="s">
         <v>987</v>
       </c>
@@ -33592,7 +33592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="938" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="938" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A938" t="s">
         <v>988</v>
       </c>
@@ -33624,7 +33624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="939" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="939" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A939" t="s">
         <v>989</v>
       </c>
@@ -33656,7 +33656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="940" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="940" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A940" t="s">
         <v>990</v>
       </c>
@@ -33688,7 +33688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="941" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="941" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A941" t="s">
         <v>991</v>
       </c>
@@ -33720,7 +33720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="942" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="942" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A942" t="s">
         <v>992</v>
       </c>
@@ -33752,7 +33752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="943" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="943" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A943" t="s">
         <v>993</v>
       </c>
@@ -33784,7 +33784,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="944" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="944" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A944" t="s">
         <v>994</v>
       </c>
@@ -33816,7 +33816,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="945" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="945" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A945" t="s">
         <v>995</v>
       </c>
@@ -33848,7 +33848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="946" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="946" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A946" t="s">
         <v>996</v>
       </c>
@@ -33880,7 +33880,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="947" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="947" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A947" t="s">
         <v>997</v>
       </c>
@@ -33912,7 +33912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="948" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="948" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A948" t="s">
         <v>998</v>
       </c>
@@ -33944,7 +33944,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="949" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="949" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A949" t="s">
         <v>999</v>
       </c>
@@ -33976,7 +33976,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="950" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="950" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A950" t="s">
         <v>1000</v>
       </c>
@@ -34008,7 +34008,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="951" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="951" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A951" t="s">
         <v>1001</v>
       </c>
@@ -34040,7 +34040,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="952" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="952" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A952" t="s">
         <v>1002</v>
       </c>
@@ -34072,7 +34072,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="953" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="953" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A953" t="s">
         <v>1003</v>
       </c>
@@ -34104,7 +34104,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="954" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="954" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A954" t="s">
         <v>1004</v>
       </c>
@@ -34136,7 +34136,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="955" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="955" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A955" t="s">
         <v>1005</v>
       </c>
@@ -34168,7 +34168,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="956" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="956" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A956" t="s">
         <v>1006</v>
       </c>
@@ -34200,7 +34200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="957" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="957" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A957" t="s">
         <v>1007</v>
       </c>
@@ -34232,7 +34232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="958" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="958" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A958" t="s">
         <v>1008</v>
       </c>
@@ -34264,7 +34264,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="959" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="959" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A959" t="s">
         <v>1009</v>
       </c>
@@ -34296,7 +34296,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="960" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="960" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A960" t="s">
         <v>1010</v>
       </c>
@@ -34328,7 +34328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="961" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="961" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A961" t="s">
         <v>1011</v>
       </c>
@@ -34360,7 +34360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="962" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="962" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A962" t="s">
         <v>1012</v>
       </c>
@@ -34392,7 +34392,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="963" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="963" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A963" t="s">
         <v>1013</v>
       </c>
@@ -34424,7 +34424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="964" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="964" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A964" t="s">
         <v>1014</v>
       </c>
@@ -34456,7 +34456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="965" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="965" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A965" t="s">
         <v>1015</v>
       </c>
@@ -34488,7 +34488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="966" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="966" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A966" t="s">
         <v>1016</v>
       </c>
@@ -34520,7 +34520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="967" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="967" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A967" t="s">
         <v>1017</v>
       </c>
@@ -34552,7 +34552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="968" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="968" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A968" t="s">
         <v>1018</v>
       </c>
@@ -34584,7 +34584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="969" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="969" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A969" t="s">
         <v>1019</v>
       </c>
@@ -34616,7 +34616,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="970" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="970" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A970" t="s">
         <v>1020</v>
       </c>
@@ -34648,7 +34648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="971" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="971" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A971" t="s">
         <v>1021</v>
       </c>
@@ -34680,7 +34680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="972" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="972" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A972" t="s">
         <v>1022</v>
       </c>
@@ -34712,7 +34712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="973" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="973" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A973" t="s">
         <v>1023</v>
       </c>
@@ -34744,7 +34744,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="974" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="974" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A974" t="s">
         <v>1024</v>
       </c>
@@ -34776,7 +34776,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="975" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="975" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A975" t="s">
         <v>1025</v>
       </c>
@@ -34808,7 +34808,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="976" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="976" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A976" t="s">
         <v>1026</v>
       </c>
@@ -34840,7 +34840,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="977" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="977" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A977" t="s">
         <v>1027</v>
       </c>
@@ -34872,7 +34872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="978" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="978" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A978" t="s">
         <v>1028</v>
       </c>
@@ -34904,7 +34904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="979" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="979" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A979" t="s">
         <v>1029</v>
       </c>
@@ -34936,7 +34936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="980" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="980" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A980" t="s">
         <v>1030</v>
       </c>
@@ -34968,7 +34968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="981" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="981" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A981" t="s">
         <v>1031</v>
       </c>
@@ -35000,7 +35000,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="982" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="982" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A982" t="s">
         <v>1032</v>
       </c>
@@ -35032,7 +35032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="983" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="983" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A983" t="s">
         <v>1033</v>
       </c>
@@ -35064,7 +35064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="984" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="984" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A984" t="s">
         <v>1034</v>
       </c>
@@ -35096,7 +35096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="985" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="985" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A985" t="s">
         <v>1035</v>
       </c>
@@ -35128,7 +35128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="986" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="986" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A986" t="s">
         <v>1036</v>
       </c>
@@ -35160,7 +35160,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="987" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="987" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A987" t="s">
         <v>1037</v>
       </c>
@@ -35192,7 +35192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="988" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="988" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A988" t="s">
         <v>1038</v>
       </c>
@@ -35224,7 +35224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="989" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="989" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A989" t="s">
         <v>1039</v>
       </c>
@@ -35256,7 +35256,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="990" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="990" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A990" t="s">
         <v>1040</v>
       </c>
@@ -35288,7 +35288,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="991" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="991" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A991" t="s">
         <v>1041</v>
       </c>
@@ -35320,7 +35320,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="992" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="992" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A992" t="s">
         <v>1042</v>
       </c>
@@ -35352,7 +35352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="993" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="993" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A993" t="s">
         <v>1043</v>
       </c>
@@ -35384,7 +35384,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="994" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="994" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A994" t="s">
         <v>1044</v>
       </c>
@@ -35416,7 +35416,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="995" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="995" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A995" t="s">
         <v>1045</v>
       </c>
@@ -35448,7 +35448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="996" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="996" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A996" t="s">
         <v>1046</v>
       </c>
@@ -35480,7 +35480,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="997" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="997" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A997" t="s">
         <v>1047</v>
       </c>
@@ -35512,7 +35512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="998" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="998" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A998" t="s">
         <v>1048</v>
       </c>
@@ -35544,7 +35544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="999" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="999" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A999" t="s">
         <v>1049</v>
       </c>
@@ -35576,7 +35576,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1000" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1000" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1000" t="s">
         <v>1050</v>
       </c>
@@ -35608,7 +35608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1001" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1001" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1001" t="s">
         <v>1051</v>
       </c>
@@ -35644,4 +35644,26 @@
   <autoFilter ref="A1:J1001" xr:uid="{88B6D82E-00BA-42F4-88DE-64444CC942E3}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ECC67DF-3AE9-4D47-BE64-220802D2550B}">
+  <dimension ref="A2:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="31.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B2">
+        <f>AVERAGE('Restaurant Sales'!J:J)</f>
+        <v>3.9180000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/2-Section- Basic Excel/data/04 Restaurant Sales.xlsx
+++ b/2-Section- Basic Excel/data/04 Restaurant Sales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a6ce4a7617f1ad9/Desktop/courses/Data Analytics/2-Section- Basic Excel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{FB2AD424-2D60-4E2A-89EA-9C030A16242E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77B5EC31-BE83-4599-8B33-A3F0485335D3}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{FB2AD424-2D60-4E2A-89EA-9C030A16242E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AC8560E-E134-4D52-8865-95A038C0AA07}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{66301FCA-EA2A-4B3B-9A5C-535C597A10AA}"/>
   </bookViews>
@@ -40,8 +40,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5011" uniqueCount="1053">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5014" uniqueCount="1056">
   <si>
     <t>Transaction ID</t>
   </si>
@@ -3200,17 +3222,27 @@
   </si>
   <si>
     <t xml:space="preserve">Average rating </t>
+  </si>
+  <si>
+    <t>Count Delivery  Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orders Types </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Categories Orders </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="[$$-C09]#,##0.00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3226,8 +3258,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3237,6 +3277,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3253,13 +3299,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3275,6 +3325,1886 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Orders</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-IN" baseline="0"/>
+              <a:t> Types</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-IN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-6654-4566-B043-F3904C32B282}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-6654-4566-B043-F3904C32B282}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-5C98-4E4F-BA3C-83A22D0BBA43}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$F$2:$F$4</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Delivery</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Takeaway</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Dine-In</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$2:$G$4</c:f>
+              <c:numCache>
+                <c:formatCode>[$$-C09]#,##0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>8457.3399999999529</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6594.4699999999757</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10747.639999999916</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5C98-4E4F-BA3C-83A22D0BBA43}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst>
+      <a:glow rad="63500">
+        <a:schemeClr val="accent4">
+          <a:satMod val="175000"/>
+          <a:alpha val="40000"/>
+        </a:schemeClr>
+      </a:glow>
+      <a:outerShdw blurRad="50800" dist="38100" dir="8100000" algn="tr" rotWithShape="0">
+        <a:prstClr val="black">
+          <a:alpha val="40000"/>
+        </a:prstClr>
+      </a:outerShdw>
+    </a:effectLst>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Categories</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-IN" baseline="0"/>
+              <a:t> Orders </a:t>
+            </a:r>
+            <a:endParaRPr lang="en-IN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.29578499562554683"/>
+          <c:y val="0.17171296296296298"/>
+          <c:w val="0.40287467191601051"/>
+          <c:h val="0.6714577865266842"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$F$7:$F$10</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Main</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Beverage</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Appetizer</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Dessert</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$7:$G$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>11994.689999999902</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2382.4099999999985</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3872.629999999991</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2418.5699999999988</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F85B-4B02-8ACF-8D3913CDAF17}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="0"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst>
+      <a:glow rad="63500">
+        <a:schemeClr val="accent1">
+          <a:satMod val="175000"/>
+          <a:alpha val="40000"/>
+        </a:schemeClr>
+      </a:glow>
+      <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+        <a:prstClr val="black">
+          <a:alpha val="40000"/>
+        </a:prstClr>
+      </a:outerShdw>
+    </a:effectLst>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>604520</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>42333</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D413B81-D065-D335-C20C-F9F710780A8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>90169</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>503767</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>5502</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{869212C1-CA0E-2611-495F-F5DCEEF03928}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -35648,13 +37578,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ECC67DF-3AE9-4D47-BE64-220802D2550B}">
-  <dimension ref="A2:B2"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.21875" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="F1" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G1" s="4"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1052</v>
       </c>
@@ -35662,8 +37600,89 @@
         <f>AVERAGE('Restaurant Sales'!J:J)</f>
         <v>3.9180000000000001</v>
       </c>
+      <c r="F2" t="str" cm="1">
+        <f t="array" ref="F2:F4">_xlfn.UNIQUE('Restaurant Sales'!D2:D1001)</f>
+        <v>Delivery</v>
+      </c>
+      <c r="G2" s="5">
+        <f>SUMIF('Restaurant Sales'!D:D, F2,'Restaurant Sales'!I:I)</f>
+        <v>8457.3399999999529</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B3">
+        <f>COUNTIF('Restaurant Sales'!D:D, "Delivery")</f>
+        <v>322</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Takeaway</v>
+      </c>
+      <c r="G3" s="5">
+        <f>SUMIF('Restaurant Sales'!D:D, F3,'Restaurant Sales'!I:I)</f>
+        <v>6594.4699999999757</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F4" t="str">
+        <v>Dine-In</v>
+      </c>
+      <c r="G4" s="5">
+        <f>SUMIF('Restaurant Sales'!D:D, F4,'Restaurant Sales'!I:I)</f>
+        <v>10747.639999999916</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="F6" s="4" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F7" t="str" cm="1">
+        <f t="array" ref="F7:F10">_xlfn.UNIQUE('Restaurant Sales'!F2:F1001)</f>
+        <v>Main</v>
+      </c>
+      <c r="G7">
+        <f ca="1">SUMIF('Restaurant Sales'!F1:F1001,F7,'Restaurant Sales'!I2:I1001)</f>
+        <v>11994.689999999902</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F8" t="str">
+        <v>Beverage</v>
+      </c>
+      <c r="G8">
+        <f>SUMIF('Restaurant Sales'!F2:F1002,F8,'Restaurant Sales'!I2:I1002)</f>
+        <v>2382.4099999999985</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F9" t="str">
+        <v>Appetizer</v>
+      </c>
+      <c r="G9">
+        <f>SUMIF('Restaurant Sales'!F3:F1003,F9,'Restaurant Sales'!I3:I1003)</f>
+        <v>3872.629999999991</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F10" t="str">
+        <v>Dessert</v>
+      </c>
+      <c r="G10">
+        <f>SUMIF('Restaurant Sales'!F4:F1004,F10,'Restaurant Sales'!I4:I1004)</f>
+        <v>2418.5699999999988</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F6:G6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>